--- a/csv_uploads/students_import.xlsx
+++ b/csv_uploads/students_import.xlsx
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>nanatenkorang.opoku@st.gimpa.edu</t>
+          <t>nanatenkorang.opoku@st.gimpa.edu.gh</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>abdul-aziz.adams@st.gimpa.edu</t>
+          <t>abdul-aziz.adams@st.gimpa.edu.gh</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
